--- a/data/trans_orig/IP07A17-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13313</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>23632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>25312</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>30487</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>45668</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>11646</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30558</t>
+          <t>30564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46344</t>
+          <t>45888</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22723</t>
+          <t>22593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>34836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>7913</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16860</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18619</t>
+          <t>18899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30580</t>
+          <t>30946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2373</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21860</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33561</t>
+          <t>34002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35441</t>
+          <t>36545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50588</t>
+          <t>51397</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17682</t>
+          <t>18025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13723</t>
+          <t>13733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24911</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>38781</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,65%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>33820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>34282</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50054</t>
+          <t>49561</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>72944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93781</t>
+          <t>93353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31801</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46885</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37153</t>
+          <t>37047</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53378</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>74245</t>
+          <t>72631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95638</t>
+          <t>94314</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>16856</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3119</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3752</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21569</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>34214</t>
+          <t>33914</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>31503</t>
+          <t>32203</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>44453</t>
+          <t>44807</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>57654</t>
+          <t>56381</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75282</t>
+          <t>74322</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21398</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37669</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>55569</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>20313</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>30929</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11442</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20570</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>34222</t>
+          <t>34860</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>48412</t>
+          <t>49043</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8942</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18363</t>
+          <t>18531</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9579</t>
+          <t>9631</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19227</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34424</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>128657</t>
+          <t>127632</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>156744</t>
+          <t>156693</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>144425</t>
+          <t>144773</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>172341</t>
+          <t>172308</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>282731</t>
+          <t>281888</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>322394</t>
+          <t>321873</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,49%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>105795</t>
+          <t>105188</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>132466</t>
+          <t>133909</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>118829</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>148846</t>
+          <t>146893</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>232166</t>
+          <t>233290</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>272161</t>
+          <t>271742</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16571</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>20373</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>36055</t>
+          <t>37223</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>41107</t>
+          <t>41489</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>64528</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2463</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21448</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31058</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45182</t>
+          <t>45862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>19108</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>17717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,85%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13828</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32363</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>46357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18929</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18531</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>33961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,64%</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6723,7 +6723,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>20564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40373</t>
+          <t>39930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27097</t>
+          <t>27688</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27152</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>41964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12026</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5995</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43681</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58761</t>
+          <t>58267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46010</t>
+          <t>45453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61846</t>
+          <t>61506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93431</t>
+          <t>93638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116245</t>
+          <t>115015</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>61,93%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>22984</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37520</t>
+          <t>36944</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>42687</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>54372</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>75700</t>
+          <t>75305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15050</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4364</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29379</t>
+          <t>29320</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>43998</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>27449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>41039</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60960</t>
+          <t>61145</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>80990</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25973</t>
+          <t>25902</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>40453</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25430</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>39073</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>55893</t>
+          <t>55265</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>75100</t>
+          <t>75205</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,25%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>14391</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4480</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>9353</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>17041</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25655</t>
+          <t>25270</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>27821</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>40958</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>66,44%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8908</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18778</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16861</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,22%</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4425</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>139489</t>
+          <t>138306</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>167052</t>
+          <t>168026</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>151504</t>
+          <t>152015</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>181269</t>
+          <t>181450</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>298754</t>
+          <t>302387</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>339072</t>
+          <t>341384</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,76%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>107526</t>
+          <t>108040</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>134979</t>
+          <t>136543</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>104180</t>
+          <t>103630</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>131990</t>
+          <t>130472</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>220461</t>
+          <t>219129</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>259909</t>
+          <t>257539</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14881</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30791</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>29602</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31534</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53128</t>
+          <t>54161</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15490</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6322</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26909</t>
+          <t>27088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>37480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6453</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17875</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>30485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>553</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3587</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20190</t>
+          <t>19824</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31828</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47654</t>
+          <t>47306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63845</t>
+          <t>63724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,45%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16081</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>27947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>17955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27078</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>755</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18939</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>17354</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44395</t>
+          <t>43984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19232</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32104</t>
+          <t>32139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>51870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>71125</t>
+          <t>70352</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51542</t>
+          <t>51658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67430</t>
+          <t>67980</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>110098</t>
+          <t>109370</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133890</t>
+          <t>134319</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,12%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50031</t>
+          <t>50682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>26785</t>
+          <t>25598</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>41974</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63315</t>
+          <t>63707</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86845</t>
+          <t>87396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,42%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13153,7 +13153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13321,7 +13321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49854</t>
+          <t>49469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>29099</t>
+          <t>28544</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43860</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>68474</t>
+          <t>69518</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89516</t>
+          <t>89184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>20017</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33930</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17929</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31140</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>41642</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60722</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15145</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4837</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6094</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14057</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>23228</t>
+          <t>23011</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>25152</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>31857</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45758</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16477</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17207</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>31820</t>
+          <t>31229</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,08%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14572,7 +14572,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>171628</t>
+          <t>171660</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>203106</t>
+          <t>202991</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>175455</t>
+          <t>171805</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>206117</t>
+          <t>205254</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>356382</t>
+          <t>356173</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>397415</t>
+          <t>397559</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>107192</t>
+          <t>107256</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>138111</t>
+          <t>137933</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>96638</t>
+          <t>95659</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>124321</t>
+          <t>126337</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>213666</t>
+          <t>214266</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>255915</t>
+          <t>254804</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>27079</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>34223</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>55808</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>5844</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1433</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>12262</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
